--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.139); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff674d83d85+79397]
-	GetHandleVerifier [0x0x7ff674d83de0+79488]
-	(No symbol) [0x0x7ff674b2c0fa]
-	(No symbol) [0x0x7ff674b82fd6]
-	(No symbol) [0x0x7ff674b8328c]
-	(No symbol) [0x0x7ff674bd6537]
-	(No symbol) [0x0x7ff674bab1df]
-	(No symbol) [0x0x7ff674bd3344]
-	(No symbol) [0x0x7ff674baaf73]
-	(No symbol) [0x0x7ff674b741b1]
-	(No symbol) [0x0x7ff674b74f43]
-	GetHandleVerifier [0x0x7ff67504e1ed+3005069]
-	GetHandleVerifier [0x0x7ff67504831d+2980797]
-	GetHandleVerifier [0x0x7ff675067e0d+3110573]
-	GetHandleVerifier [0x0x7ff674d9d6de+184190]
-	GetHandleVerifier [0x0x7ff674da516f+215567]
-	GetHandleVerifier [0x0x7ff674d8c974+115220]
-	GetHandleVerifier [0x0x7ff674d8cb29+115657]
-	GetHandleVerifier [0x0x7ff674d73268+11016]
+	GetHandleVerifier [0x0x7ff6e4ec3d85+79397]
+	GetHandleVerifier [0x0x7ff6e4ec3de0+79488]
+	(No symbol) [0x0x7ff6e4c6c0fa]
+	(No symbol) [0x0x7ff6e4cc2fd6]
+	(No symbol) [0x0x7ff6e4cc328c]
+	(No symbol) [0x0x7ff6e4d16537]
+	(No symbol) [0x0x7ff6e4ceb1df]
+	(No symbol) [0x0x7ff6e4d13344]
+	(No symbol) [0x0x7ff6e4ceaf73]
+	(No symbol) [0x0x7ff6e4cb41b1]
+	(No symbol) [0x0x7ff6e4cb4f43]
+	GetHandleVerifier [0x0x7ff6e518e1ed+3005069]
+	GetHandleVerifier [0x0x7ff6e518831d+2980797]
+	GetHandleVerifier [0x0x7ff6e51a7e0d+3110573]
+	GetHandleVerifier [0x0x7ff6e4edd6de+184190]
+	GetHandleVerifier [0x0x7ff6e4ee516f+215567]
+	GetHandleVerifier [0x0x7ff6e4ecc974+115220]
+	GetHandleVerifier [0x0x7ff6e4eccb29+115657]
+	GetHandleVerifier [0x0x7ff6e4eb3268+11016]
 	BaseThreadInitThunk [0x0x7ffd0f98e8d7+23]
 	RtlUserThreadStart [0x0x7ffd11a3c34c+44]
 </t>
